--- a/data/office/efem-cost-reduction-tracker.xlsx
+++ b/data/office/efem-cost-reduction-tracker.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="D3" t="n">
         <v>18000</v>
@@ -655,7 +655,7 @@
         <v>366000</v>
       </c>
       <c r="C2" t="n">
-        <v>334500</v>
+        <v>334300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34000</v>
+        <v>34200</v>
       </c>
       <c r="C8" t="n">
         <v>28500</v>
